--- a/products-storage/00-free-dopy-ne-v-podarok/04-reestr-doprabot.xlsx
+++ b/products-storage/00-free-dopy-ne-v-podarok/04-reestr-doprabot.xlsx
@@ -513,23 +513,19 @@
           <t>Пример: Устройство отмостки</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="D2" s="2" t="n">
+        <v>150</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>м2</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
+      <c r="F2" s="2" t="n">
+        <v>850</v>
       </c>
       <c r="G2" s="2">
-        <f>G2*D2</f>
+        <f>IF(OR(D2="",F2=""),"",D2*F2)</f>
         <v/>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -549,7 +545,10 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" s="2">
+        <f>IF(OR(D3="",F3=""),"",D3*F3)</f>
+        <v/>
+      </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
@@ -563,7 +562,10 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="2">
+        <f>IF(OR(D4="",F4=""),"",D4*F4)</f>
+        <v/>
+      </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
@@ -580,7 +582,7 @@
         </is>
       </c>
       <c r="G5" s="2">
-        <f>SUM(G2:G10)</f>
+        <f>SUM(G2:G4)</f>
         <v/>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
